--- a/product_selector_out/STM32L4x6.xlsx
+++ b/product_selector_out/STM32L4x6.xlsx
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AW12" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX12" s="4" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AW13" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX13" s="4" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AW14" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX14" s="4" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AW15" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX15" s="4" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AW16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX16" s="4" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="AW17" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX17" s="4" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AW18" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX18" s="4" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AW19" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX19" s="4" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AW20" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX20" s="4" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AW21" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX21" s="4" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="AW22" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX22" s="4" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="AW23" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX23" s="4" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="AW24" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX24" s="4" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="AW25" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX25" s="4" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="AW26" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX26" s="4" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="AW27" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX27" s="4" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AW28" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX28" s="4" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="AW29" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX29" s="4" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="AW30" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX30" s="4" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="AW31" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX31" s="4" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="AW32" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX32" s="4" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="AW33" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX33" s="4" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AW34" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX34" s="4" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="AW35" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX35" s="4" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="AW36" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX36" s="4" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="AW37" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX37" s="4" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="AW38" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX38" s="4" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="AW39" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX39" s="4" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="AW40" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX40" s="4" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="AW41" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX41" s="4" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="AW42" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX42" s="4" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="AW43" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX43" s="4" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="AW44" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX44" s="4" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="AW45" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX45" s="4" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="AW46" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX46" s="4" t="inlineStr">
@@ -13295,9 +13295,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX12" s="7" t="inlineStr">
@@ -13622,9 +13622,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX13" s="7" t="inlineStr">
@@ -13949,9 +13949,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX14" s="7" t="inlineStr">
@@ -14276,9 +14276,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX15" s="7" t="inlineStr">
@@ -14383,9 +14383,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -14448,14 +14448,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -14603,14 +14603,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -14683,9 +14683,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -14930,9 +14930,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX17" s="7" t="inlineStr">
@@ -15257,9 +15257,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX18" s="7" t="inlineStr">
@@ -15584,9 +15584,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX19" s="7" t="inlineStr">
@@ -15911,9 +15911,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX20" s="7" t="inlineStr">
@@ -16238,9 +16238,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX21" s="7" t="inlineStr">
@@ -16345,9 +16345,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -16410,14 +16410,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -16565,14 +16565,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY22" s="6" t="inlineStr">
@@ -16645,9 +16645,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -16672,9 +16672,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -16737,14 +16737,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -16892,14 +16892,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -16972,9 +16972,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -17219,9 +17219,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX24" s="7" t="inlineStr">
@@ -17326,9 +17326,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -17391,14 +17391,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
@@ -17546,14 +17546,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY25" s="6" t="inlineStr">
@@ -17626,9 +17626,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -17873,9 +17873,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX26" s="7" t="inlineStr">
@@ -18200,9 +18200,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX27" s="7" t="inlineStr">
@@ -18527,9 +18527,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX28" s="7" t="inlineStr">
@@ -18854,9 +18854,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX29" s="7" t="inlineStr">
@@ -19181,9 +19181,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX30" s="7" t="inlineStr">
@@ -19508,9 +19508,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX31" s="7" t="inlineStr">
@@ -19835,9 +19835,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX32" s="7" t="inlineStr">
@@ -20162,9 +20162,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX33" s="7" t="inlineStr">
@@ -20489,9 +20489,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX34" s="7" t="inlineStr">
@@ -20816,9 +20816,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX35" s="7" t="inlineStr">
@@ -21143,9 +21143,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW36" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX36" s="7" t="inlineStr">
@@ -21470,9 +21470,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX37" s="7" t="inlineStr">
@@ -21797,9 +21797,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW38" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX38" s="7" t="inlineStr">
@@ -22124,9 +22124,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW39" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX39" s="7" t="inlineStr">
@@ -22451,9 +22451,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX40" s="7" t="inlineStr">
@@ -22778,9 +22778,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW41" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX41" s="7" t="inlineStr">
@@ -23105,9 +23105,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX42" s="7" t="inlineStr">
@@ -23432,9 +23432,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX43" s="7" t="inlineStr">
@@ -23759,9 +23759,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX44" s="7" t="inlineStr">
@@ -24086,9 +24086,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW45" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX45" s="7" t="inlineStr">
@@ -24413,9 +24413,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW46" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX46" s="7" t="inlineStr">
@@ -24514,7 +24514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -24592,12 +24592,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32L476RC</t>
+          <t>STM32L476JE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -24607,7 +24607,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24619,7 +24619,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -24636,12 +24636,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32L4A6AG</t>
+          <t>STM32L476RC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -24651,19 +24651,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32L4A6AG</t>
+          <t>STM32L476RC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -24673,19 +24673,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32L486ZG</t>
+          <t>STM32L4A6AG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -24695,19 +24695,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32L486ZG</t>
+          <t>STM32L4A6AG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -24717,19 +24717,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32L486ZG</t>
+          <t>STM32L4A6AG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -24739,19 +24739,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32L4A6ZG</t>
+          <t>STM32L486ZG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -24761,19 +24761,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32L4A6ZG</t>
+          <t>STM32L486ZG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -24783,19 +24783,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32L476JG</t>
+          <t>STM32L486ZG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -24805,19 +24805,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32L476JG</t>
+          <t>STM32L486ZG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -24827,19 +24827,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32L486QG</t>
+          <t>STM32L476JG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -24849,19 +24849,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32L486QG</t>
+          <t>STM32L476JG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -24871,19 +24871,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32L486QG</t>
+          <t>STM32L476JG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -24893,19 +24893,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32L496QE</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -24915,19 +24915,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32L496QE</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -24937,19 +24937,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32L486JG</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -24959,19 +24959,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists WLCSP72 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32L486JG</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -24981,19 +24981,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L486JG</t>
+          <t>STM32L496QE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -25003,19 +25003,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L496QE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -25025,19 +25025,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L496QE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -25047,19 +25047,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -25069,19 +25069,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists WLCSP72 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L4A6QG</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -25091,19 +25091,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L4A6QG</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -25113,19 +25113,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L4A6VG</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -25135,19 +25135,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L4A6VG</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -25157,19 +25157,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L476VC</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -25179,19 +25179,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L476VC</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -25201,19 +25201,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L4A6RG</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -25223,19 +25223,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L4A6RG</t>
+          <t>STM32L476VC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -25245,19 +25245,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L476QG</t>
+          <t>STM32L476VC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -25274,12 +25274,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L476QG</t>
+          <t>STM32L476VC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -25289,14 +25289,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L496VE</t>
+          <t>STM32L476QG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -25311,14 +25311,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L496VE</t>
+          <t>STM32L476QG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -25333,19 +25333,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L476VG</t>
+          <t>STM32L476QG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -25355,19 +25355,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L476VG</t>
+          <t>STM32L496VE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -25377,19 +25377,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L496RE</t>
+          <t>STM32L496VE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -25406,12 +25406,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L496RE</t>
+          <t>STM32L496VE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -25421,14 +25421,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L476RG</t>
+          <t>STM32L476VG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -25450,7 +25450,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32L476RG</t>
+          <t>STM32L476VG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -25472,12 +25472,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L496AE</t>
+          <t>STM32L476VG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -25487,19 +25487,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L496AE</t>
+          <t>STM32L496RE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -25516,12 +25516,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L496ZE</t>
+          <t>STM32L496RE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -25538,12 +25538,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32L496ZE</t>
+          <t>STM32L496RE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -25553,14 +25553,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L476ZE</t>
+          <t>STM32L476RG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -25582,7 +25582,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L476ZE</t>
+          <t>STM32L476RG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -25604,12 +25604,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L476ZG</t>
+          <t>STM32L476RG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -25619,19 +25619,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L476ZG</t>
+          <t>STM32L496AE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -25641,19 +25641,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L496VG</t>
+          <t>STM32L496AE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -25670,12 +25670,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32L496VG</t>
+          <t>STM32L496AE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -25685,14 +25685,14 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32L496QG</t>
+          <t>STM32L496ZE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -25714,7 +25714,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32L496QG</t>
+          <t>STM32L496ZE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -25736,12 +25736,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32L476MG</t>
+          <t>STM32L496ZE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -25751,19 +25751,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L476MG</t>
+          <t>STM32L476ZE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -25780,12 +25780,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L496AG</t>
+          <t>STM32L476ZE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -25795,19 +25795,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L496AG</t>
+          <t>STM32L476ZE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -25817,14 +25817,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L476QE</t>
+          <t>STM32L476ZG</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -25846,7 +25846,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L476QE</t>
+          <t>STM32L476ZG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -25868,12 +25868,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L476VE</t>
+          <t>STM32L476ZG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -25883,19 +25883,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L476VE</t>
+          <t>STM32L496VG</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -25905,19 +25905,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L476RE</t>
+          <t>STM32L496VG</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -25927,19 +25927,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L476RE</t>
+          <t>STM32L496VG</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -25949,14 +25949,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L496RG</t>
+          <t>STM32L496QG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -25978,7 +25978,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L496RG</t>
+          <t>STM32L496QG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -26000,12 +26000,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L496ZG</t>
+          <t>STM32L496QG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -26015,19 +26015,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L496ZG</t>
+          <t>STM32L476MG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -26037,19 +26037,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L476ME</t>
+          <t>STM32L476MG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -26066,12 +26066,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32L476ME</t>
+          <t>STM32L476MG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -26081,19 +26081,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L496AG</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -26103,19 +26103,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L496AG</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -26125,19 +26125,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L496AG</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -26147,14 +26147,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32L496WG</t>
+          <t>STM32L476QE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -26169,29 +26169,535 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>STM32L476QE</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>STM32L476QE</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>STM32L476VE</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STM32L476VE</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>STM32L476VE</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>STM32L476RE</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>STM32L476RE</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>STM32L476RE</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>STM32L496RG</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>STM32L496RG</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>STM32L496RG</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>STM32L496ZG</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>STM32L496ZG</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>STM32L496ZG</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>STM32L476ME</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>STM32L476ME</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>STM32L476ME</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
           <t>STM32L496WG</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>STM32L496WG</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
         <is>
           <t>Timers (32-bit) typ</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>STM32L496WG</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32L4x6.xlsx
+++ b/product_selector_out/STM32L4x6.xlsx
@@ -2628,7 +2628,7 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
     </row>
@@ -14383,9 +14383,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -14448,14 +14448,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -14603,14 +14603,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -14683,9 +14683,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -16345,9 +16345,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -16410,14 +16410,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -16565,14 +16565,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY22" s="6" t="inlineStr">
@@ -16645,9 +16645,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -16672,9 +16672,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -16737,14 +16737,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -16892,14 +16892,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -16972,9 +16972,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -17326,9 +17326,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -17391,14 +17391,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
@@ -17546,14 +17546,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY25" s="6" t="inlineStr">
@@ -17626,9 +17626,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -24514,7 +24514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -24834,7 +24834,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32L476JG</t>
+          <t>STM32L4A6ZG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -24849,14 +24849,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32L476JG</t>
+          <t>STM32L4A6ZG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -24871,14 +24871,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32L476JG</t>
+          <t>STM32L4A6ZG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -24893,19 +24893,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32L486QG</t>
+          <t>STM32L476JG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -24915,19 +24915,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32L486QG</t>
+          <t>STM32L476JG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -24937,14 +24937,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32L486QG</t>
+          <t>STM32L476JG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -24981,19 +24981,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L496QE</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -25003,19 +25003,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L496QE</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -25025,19 +25025,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L496QE</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -25047,19 +25047,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32L486JG</t>
+          <t>STM32L496QE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -25069,19 +25069,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists WLCSP72 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L486JG</t>
+          <t>STM32L496QE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -25091,14 +25091,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L486JG</t>
+          <t>STM32L496QE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -25113,7 +25113,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -25125,7 +25125,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -25135,19 +25135,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists WLCSP72 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -25157,19 +25157,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -25179,19 +25179,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -25201,7 +25201,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -25213,7 +25213,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -25223,19 +25223,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L476VC</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -25245,19 +25245,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L476VC</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -25267,19 +25267,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L476VC</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -25289,14 +25289,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L476QG</t>
+          <t>STM32L4A6QG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -25311,14 +25311,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L476QG</t>
+          <t>STM32L4A6QG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -25333,14 +25333,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L476QG</t>
+          <t>STM32L4A6QG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -25355,14 +25355,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L496VE</t>
+          <t>STM32L4A6VG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -25384,7 +25384,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L496VE</t>
+          <t>STM32L4A6VG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -25406,7 +25406,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L496VE</t>
+          <t>STM32L4A6VG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -25428,7 +25428,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L476VG</t>
+          <t>STM32L476VC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -25450,7 +25450,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32L476VG</t>
+          <t>STM32L476VC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -25472,7 +25472,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L476VG</t>
+          <t>STM32L476VC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -25494,7 +25494,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L496RE</t>
+          <t>STM32L4A6RG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L496RE</t>
+          <t>STM32L4A6RG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -25538,7 +25538,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32L496RE</t>
+          <t>STM32L4A6RG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -25560,7 +25560,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L476RG</t>
+          <t>STM32L476QG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -25582,7 +25582,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L476RG</t>
+          <t>STM32L476QG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -25604,7 +25604,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L476RG</t>
+          <t>STM32L476QG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -25626,7 +25626,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L496AE</t>
+          <t>STM32L496VE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -25648,7 +25648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L496AE</t>
+          <t>STM32L496VE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -25670,7 +25670,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32L496AE</t>
+          <t>STM32L496VE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -25692,7 +25692,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32L496ZE</t>
+          <t>STM32L476VG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -25707,14 +25707,14 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32L496ZE</t>
+          <t>STM32L476VG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -25729,14 +25729,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32L496ZE</t>
+          <t>STM32L476VG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -25751,14 +25751,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L476ZE</t>
+          <t>STM32L496RE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25773,14 +25773,14 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L476ZE</t>
+          <t>STM32L496RE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25795,14 +25795,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L476ZE</t>
+          <t>STM32L496RE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25817,14 +25817,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L476ZG</t>
+          <t>STM32L476RG</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -25846,7 +25846,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L476ZG</t>
+          <t>STM32L476RG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -25868,7 +25868,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L476ZG</t>
+          <t>STM32L476RG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -25890,7 +25890,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L496VG</t>
+          <t>STM32L496AE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -25912,7 +25912,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L496VG</t>
+          <t>STM32L496AE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -25934,7 +25934,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L496VG</t>
+          <t>STM32L496AE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -25956,7 +25956,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L496QG</t>
+          <t>STM32L496ZE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -25978,7 +25978,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L496QG</t>
+          <t>STM32L496ZE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -26000,7 +26000,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L496QG</t>
+          <t>STM32L496ZE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -26022,7 +26022,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L476MG</t>
+          <t>STM32L476ZE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L476MG</t>
+          <t>STM32L476ZE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -26066,7 +26066,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32L476MG</t>
+          <t>STM32L476ZE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -26088,7 +26088,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32L496AG</t>
+          <t>STM32L476ZG</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -26103,14 +26103,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32L496AG</t>
+          <t>STM32L476ZG</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -26125,14 +26125,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32L496AG</t>
+          <t>STM32L476ZG</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -26147,14 +26147,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32L476QE</t>
+          <t>STM32L496VG</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -26169,14 +26169,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32L476QE</t>
+          <t>STM32L496VG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -26191,14 +26191,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32L476QE</t>
+          <t>STM32L496VG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -26213,14 +26213,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32L476VE</t>
+          <t>STM32L496QG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -26235,14 +26235,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32L476VE</t>
+          <t>STM32L496QG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -26257,14 +26257,14 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32L476VE</t>
+          <t>STM32L496QG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -26279,14 +26279,14 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32L476RE</t>
+          <t>STM32L476MG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32L476RE</t>
+          <t>STM32L476MG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -26330,7 +26330,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32L476RE</t>
+          <t>STM32L476MG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -26352,7 +26352,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32L496RG</t>
+          <t>STM32L496AG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -26374,7 +26374,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32L496RG</t>
+          <t>STM32L496AG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -26396,7 +26396,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32L496RG</t>
+          <t>STM32L496AG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -26418,7 +26418,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32L496ZG</t>
+          <t>STM32L476QE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -26433,14 +26433,14 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32L496ZG</t>
+          <t>STM32L476QE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -26455,14 +26455,14 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32L496ZG</t>
+          <t>STM32L476QE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -26477,14 +26477,14 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32L476ME</t>
+          <t>STM32L476VE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -26506,7 +26506,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32L476ME</t>
+          <t>STM32L476VE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -26528,7 +26528,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32L476ME</t>
+          <t>STM32L476VE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -26550,12 +26550,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L476RE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -26565,19 +26565,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L476RE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -26587,14 +26587,14 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L476RE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -26616,12 +26616,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L496RG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -26631,19 +26631,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32L496WG</t>
+          <t>STM32L496RG</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -26660,12 +26660,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32L496WG</t>
+          <t>STM32L496RG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -26675,27 +26675,291 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>STM32L496ZG</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>STM32L496ZG</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>STM32L496ZG</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>STM32L476ME</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>STM32L476ME</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>STM32L476ME</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
           <t>STM32L496WG</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>STM32L496WG</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>STM32L496WG</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32L4x6.xlsx
+++ b/product_selector_out/STM32L4x6.xlsx
@@ -2066,7 +2066,7 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S45" s="4" t="inlineStr">
@@ -14136,14 +14136,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W15" s="8" t="inlineStr">
@@ -14166,9 +14166,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="6" t="inlineStr">
@@ -14226,9 +14226,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr">
@@ -15117,14 +15117,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W18" s="8" t="inlineStr">
@@ -15147,9 +15147,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB18" s="6" t="inlineStr">
@@ -15207,9 +15207,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN18" s="6" t="inlineStr">
@@ -15771,14 +15771,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W20" s="8" t="inlineStr">
@@ -15801,9 +15801,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB20" s="6" t="inlineStr">
@@ -15861,9 +15861,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN20" s="6" t="inlineStr">
@@ -16098,14 +16098,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W21" s="8" t="inlineStr">
@@ -16128,9 +16128,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB21" s="6" t="inlineStr">
@@ -16188,9 +16188,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN21" s="6" t="inlineStr">
@@ -23946,14 +23946,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W45" s="8" t="inlineStr">
@@ -23976,9 +23976,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB45" s="6" t="inlineStr">
@@ -24036,9 +24036,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM45" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN45" s="6" t="inlineStr">

--- a/product_selector_out/STM32L4x6.xlsx
+++ b/product_selector_out/STM32L4x6.xlsx
@@ -14226,9 +14226,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr">
@@ -15207,9 +15207,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN18" s="6" t="inlineStr">
@@ -15861,9 +15861,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN20" s="6" t="inlineStr">
@@ -16188,9 +16188,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN21" s="6" t="inlineStr">
@@ -24036,9 +24036,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN45" s="6" t="inlineStr">

--- a/product_selector_out/STM32L4x6.xlsx
+++ b/product_selector_out/STM32L4x6.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM46"/>
+  <dimension ref="A1:BN46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9609375" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l486jg.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l486jg.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l486jg.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l486jg.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
@@ -4917,6 +4979,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
@@ -5244,6 +5311,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -5571,6 +5643,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
@@ -5898,6 +5975,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -6225,6 +6307,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -6552,6 +6639,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -6879,6 +6971,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -7206,6 +7303,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -7533,6 +7635,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -7860,6 +7967,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -8187,6 +8299,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -8514,6 +8631,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -8841,6 +8963,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -9168,6 +9295,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -9495,6 +9627,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -9822,6 +9959,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -10149,6 +10291,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -10476,6 +10623,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -10803,6 +10955,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -11130,6 +11287,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -11457,6 +11619,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -11784,6 +11951,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -12111,6 +12283,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l486jg.pdf</t>
         </is>
       </c>
@@ -12438,12 +12615,17 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -12464,16 +12646,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -12486,6 +12666,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -12505,7 +12686,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -12557,7 +12740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM46"/>
+  <dimension ref="A1:BN46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12625,6 +12808,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12958,6 +13142,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -13053,6 +13242,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -13375,7 +13565,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13702,7 +13897,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14029,7 +14229,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14356,7 +14561,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14683,7 +14893,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15010,7 +15225,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15337,7 +15557,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15664,7 +15889,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15991,7 +16221,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16318,7 +16553,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16645,7 +16885,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16972,7 +17217,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17299,7 +17549,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17626,7 +17881,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17953,7 +18213,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18280,7 +18545,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18607,7 +18877,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18934,7 +19209,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19261,7 +19541,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19588,7 +19873,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19915,7 +20205,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20242,7 +20537,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20569,7 +20869,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20896,7 +21201,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21223,7 +21533,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21550,7 +21865,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21877,7 +22197,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22204,7 +22529,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22531,7 +22861,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22858,7 +23193,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23185,7 +23525,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23512,7 +23857,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23839,7 +24189,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24166,7 +24521,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24493,7 +24853,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
+      <c r="BM46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24501,8 +24866,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
